--- a/data_long_lat.xlsx
+++ b/data_long_lat.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MODUL STATCAL\WEBSITE STATCAL\Member of STATCAL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MODUL STATCAL\WEBSITE STATCAL\Member of STATCAL\testing 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{197E0D71-BA0D-4CD5-B7EF-0CB83296985F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B0B8687-C36F-4CD8-BDA3-5541286AFB69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -432,7 +432,7 @@
         <v>-6.4058200000000003</v>
       </c>
       <c r="D4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
